--- a/r4-ELGA-e-Diagnose-ballot_2026_03/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-ballot_2026_03/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:47:52+00:00</t>
+    <t>2026-10-27T15:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-ballot_2026_03/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-ballot_2026_03/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T15:15:47+00:00</t>
+    <t>2026-10-28T08:34:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-ballot_2026_03/ValueSet-at-ediag-allergyintolerance-code.xlsx
+++ b/r4-ELGA-e-Diagnose-ballot_2026_03/ValueSet-at-ediag-allergyintolerance-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T08:34:30+00:00</t>
+    <t>2026-10-28T08:57:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
